--- a/negative_reviews_enbd_bank_branches_10May2026.xlsx
+++ b/negative_reviews_enbd_bank_branches_10May2026.xlsx
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46152.8338437819</v>
+        <v>46152.81686866551</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
